--- a/backend/data/uploads/MES/2026-07-22_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-22_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F029B7A9-6373-4CA1-87DB-5BE491642210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{060176B2-9F99-43A7-A89B-0F7D7947BF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{01464363-C198-4E0E-9740-3ACCA1C7B6F0}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{682EB703-6182-47A2-9DD5-0C2854AF282D}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C66F766-C406-447B-ACB4-8FD480054754}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD502EDA-0FED-47F5-8E7E-3C0D318D3E54}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
